--- a/Result/profitability/9940.xlsx
+++ b/Result/profitability/9940.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.34625</v>
+        <v>0.33375</v>
       </c>
       <c r="N2" t="n">
-        <v>23.38875</v>
+        <v>23.955</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4425</v>
+        <v>0.4575</v>
       </c>
       <c r="N3" t="n">
-        <v>24.82625</v>
+        <v>25.0275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42375</v>
+        <v>0.465</v>
       </c>
       <c r="N4" t="n">
-        <v>23.755</v>
+        <v>24.65875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4275</v>
+        <v>0.505</v>
       </c>
       <c r="N5" t="n">
-        <v>23.72</v>
+        <v>25.02625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.49</v>
+        <v>0.53125</v>
       </c>
       <c r="N6" t="n">
-        <v>24.79875</v>
+        <v>25.3125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.675</v>
+        <v>0.70625</v>
       </c>
       <c r="N7" t="n">
-        <v>26.9975</v>
+        <v>28.4275</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>0.81125</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>29.28125</v>
+        <v>29.9325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3059</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2192</v>
+      </c>
+      <c r="E75" t="n">
+        <v>867</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>378</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.34%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>62</v>
+      </c>
+      <c r="J75" t="n">
+        <v>440</v>
+      </c>
+      <c r="K75" t="n">
+        <v>329</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.7575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.209999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2253460207612457</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.647058823529412</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.5844519015659955</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
